--- a/docs/요구사항정의서.xlsx
+++ b/docs/요구사항정의서.xlsx
@@ -12,7 +12,7 @@
     <sheet name="기능적_요구사항" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="비기능적_요구사항" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="제약사항_예상결과" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Codex_실습범위" sheetId="6" r:id="Rcf74326b8d7e401a"/>
+    <sheet name="RAG_구현범위" sheetId="6" r:id="Rcf74326b8d7e401a"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'이해관계자_식별'!$A$1:$F$9</definedName>
@@ -847,7 +847,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>최초 작성 (Day04 가설·KPI 기반)</t>
+          <t>최초 작성 (가설·KPI 기반)</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>설문/인터뷰(Day03)</t>
+          <t>설문/인터뷰</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Day03 조사 출처</t>
+          <t>조사 출처</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>Day02 Pain Point</t>
+          <t>Pain Point</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr"/>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Day03 데이터 조사</t>
+          <t>데이터 조사</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>Day02 Pain Point</t>
+          <t>Pain Point</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr"/>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>Day03 데이터 조사</t>
+          <t>데이터 조사</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>근거 인용 필수(Day04 가설수립)</t>
+          <t>근거 인용 필수(가설수립)</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>Day04 KPI 설계</t>
+          <t>KPI 설계</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr"/>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>Day04 가설수립</t>
+          <t>가설수립</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>Day02 Pain Point</t>
+          <t>Pain Point</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr"/>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>4주 내 MVP 출시 목표 (Day04 KPI 측정 시점 기준)</t>
+          <t>4주 내 MVP 출시 목표 (KPI 측정 시점 기준)</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Day04 KPI 목표 달성 시 상세페이지 진입 소요시간 30% 감소, 재질문 비율 20% 감소, 상담 완료율 70% 이상, 과다섭취 CS 문의 25% 감소</t>
+          <t>KPI 목표 달성 시 상세페이지 진입 소요시간 30% 감소, 재질문 비율 20% 감소, 상담 완료율 70% 이상, 과다섭취 CS 문의 25% 감소</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr"/>
@@ -3154,12 +3154,13 @@
     <col min="3" max="3" width="30" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="24" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="64" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="12" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="28" t="str">
-        <v>실습ID</v>
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>요구사항ID</t>
+        </is>
       </c>
       <c r="B1" s="28" t="str">
         <v>원문 연결</v>
@@ -3167,14 +3168,13 @@
       <c r="C1" s="28" t="str">
         <v>요구사항</v>
       </c>
-      <c r="D1" s="28" t="str">
-        <v>이번 강의 범위</v>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>첫 버전 범위</t>
+        </is>
       </c>
       <c r="E1" s="28" t="str">
         <v>완료 기준</v>
-      </c>
-      <c r="F1" s="28" t="str">
-        <v>장</v>
       </c>
     </row>
     <row r="2" ht="38" customHeight="1">
@@ -3193,9 +3193,6 @@
       <c r="E2" s="24" t="str">
         <v>공백 제거 후 1~1000자. 빈 입력·초과는 422.</v>
       </c>
-      <c r="F2" s="24" t="str">
-        <v>3~5</v>
-      </c>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="A3" s="24" t="str">
@@ -3213,9 +3210,6 @@
       <c r="E3" s="24" t="str">
         <v>검수한 문서만 검색. 문단 최대 3개, 동점 순서 고정.</v>
       </c>
-      <c r="F3" s="24" t="str">
-        <v>3~5</v>
-      </c>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="A4" s="24" t="str">
@@ -3233,9 +3227,6 @@
       <c r="E4" s="24" t="str">
         <v>검색 근거로만 생성. 모의 테스트와 실제 호출 구분.</v>
       </c>
-      <c r="F4" s="24" t="str">
-        <v>3~5</v>
-      </c>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="24" t="str">
@@ -3253,16 +3244,15 @@
       <c r="E5" s="24" t="str">
         <v>선택 문단의 ID만 허용. 출처와 위치를 서버에서 구성.</v>
       </c>
-      <c r="F5" s="24" t="str">
-        <v>3~5</v>
-      </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="A6" s="24" t="str">
         <v>LAB-RAG-05</v>
       </c>
-      <c r="B6" s="24" t="str">
-        <v>수업 추가 결정</v>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>추가 요구사항</t>
+        </is>
       </c>
       <c r="C6" s="24" t="str">
         <v>근거 부족 처리</v>
@@ -3272,17 +3262,16 @@
       </c>
       <c r="E6" s="24" t="str">
         <v>검색 결과가 없으면 LLM 미호출. 부족 안내와 빈 인용 반환.</v>
-      </c>
-      <c r="F6" s="24" t="str">
-        <v>3~5</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="A7" s="24" t="str">
         <v>LAB-RAG-06</v>
       </c>
-      <c r="B7" s="24" t="str">
-        <v>수업 추가 결정</v>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>추가 요구사항</t>
+        </is>
       </c>
       <c r="C7" s="24" t="str">
         <v>장애·잘못된 생성 결과 처리</v>
@@ -3292,9 +3281,6 @@
       </c>
       <c r="E7" s="24" t="str">
         <v>503 unavailable. 실패를 성공 답변이나 stub으로 숨기지 않음.</v>
-      </c>
-      <c r="F7" s="24" t="str">
-        <v>3~5</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
@@ -3313,9 +3299,6 @@
       <c r="E8" s="24" t="str">
         <v>질문·답변·출처·상태 표시. 상품 조회와 페이지 이동 유지.</v>
       </c>
-      <c r="F8" s="24" t="str">
-        <v>3~5</v>
-      </c>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="A9" s="24" t="str">
@@ -3333,9 +3316,6 @@
       <c r="E9" s="24" t="str">
         <v>로그에 질문·키를 기록하지 않음. 대화는 화면 세션에만 보관.</v>
       </c>
-      <c r="F9" s="24" t="str">
-        <v>2~5</v>
-      </c>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="A10" s="24" t="str">
@@ -3347,22 +3327,23 @@
       <c r="C10" s="24" t="str">
         <v>응답시간 측정</v>
       </c>
-      <c r="D10" s="24" t="str">
-        <v>관찰·개선 과제</v>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>관찰·개선 항목</t>
+        </is>
       </c>
       <c r="E10" s="24" t="str">
         <v>실제 환경·모델·시간 기록. 원문 5초 목표의 충족을 단정하지 않음.</v>
-      </c>
-      <c r="F10" s="24" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="A11" s="24" t="str">
         <v>LAB-DEV-01</v>
       </c>
-      <c r="B11" s="24" t="str">
-        <v>수업 추가 결정</v>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>추가 요구사항</t>
+        </is>
       </c>
       <c r="C11" s="24" t="str">
         <v>기존 기능 보존</v>
@@ -3372,17 +3353,16 @@
       </c>
       <c r="E11" s="24" t="str">
         <v>기존 22개 테스트와 상품 44개 조회·페이지 이동 유지.</v>
-      </c>
-      <c r="F11" s="24" t="str">
-        <v>2~5</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1">
       <c r="A12" s="24" t="str">
         <v>LAB-DEV-02</v>
       </c>
-      <c r="B12" s="24" t="str">
-        <v>수업 추가 결정</v>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>추가 요구사항</t>
+        </is>
       </c>
       <c r="C12" s="24" t="str">
         <v>검증·커밋·PR</v>
@@ -3392,9 +3372,6 @@
       </c>
       <c r="E12" s="24" t="str">
         <v>테스트·Ruff·리뷰 후 관련 파일 커밋. PR·CI·수정 근거 기록.</v>
-      </c>
-      <c r="F12" s="24" t="str">
-        <v>4~5</v>
       </c>
     </row>
     <row r="13" ht="38" customHeight="1">
@@ -3407,14 +3384,15 @@
       <c r="C13" s="24" t="str">
         <v>추천·성분 설명·CS·복용량</v>
       </c>
-      <c r="D13" s="24" t="str">
-        <v>이번 과정 제외</v>
-      </c>
-      <c r="E13" s="24" t="str">
-        <v>원문 요구사항은 아래 기존 시트에 보존. 완료했다고 보고하지 않음.</v>
-      </c>
-      <c r="F13" s="24" t="str">
-        <v>후속</v>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>첫 버전 제외</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>원문 요구사항은 기존 시트에 보존. 완료했다고 보고하지 않음.</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="38" customHeight="1">
@@ -3432,9 +3410,6 @@
       </c>
       <c r="E14" s="24" t="str">
         <v>민감한 입력을 저장하지 않는 첫 버전. 운영 서비스 보안 완료와 구분.</v>
-      </c>
-      <c r="F14" s="24" t="str">
-        <v>후속</v>
       </c>
     </row>
   </sheetData>
